--- a/artfynd/A 11373-2026 artfynd.xlsx
+++ b/artfynd/A 11373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91938172</v>
+        <v>2073893</v>
       </c>
       <c r="B2" t="n">
-        <v>81962</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>232272</v>
+        <v>6471</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Årås NR Kohestervägen, Vg</t>
+          <t>Årås, träd 16152 (ask), Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>419528.6982785402</v>
+        <v>419597</v>
       </c>
       <c r="R2" t="n">
-        <v>6416789.570046457</v>
+        <v>6416850</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-12-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2006-12-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>(ss. S. nivea)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,22 +759,358 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # ask</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ingvar Claesson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2073894</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Årås, träd 16140 (lönn), Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>419458</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6416764</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kölingared</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2006-12-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2006-12-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>(ss. S. nivea)</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # lönn</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ingvar Claesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>83337475</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>VGL Träd ID: 16152, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>419597</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6416850</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kölingared</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>8DF3A136-C274-4AF8-8CC4-7DCCF4DB143A</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2006-12-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2006-12-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Sjögren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Sjögren, Ingvar Claesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>91938172</v>
+      </c>
+      <c r="B5" t="n">
+        <v>84148</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>232272</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcoscypha austriaca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Årås NR Kohestervägen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>419529</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6416790</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kölingared</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-03-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-03-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Susanne Hernqvist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Susanne Hernqvist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11373-2026 artfynd.xlsx
+++ b/artfynd/A 11373-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2073893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>Epifyt-inv. Särskilt skyddsvärda träd 2005-2007</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2073894</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83337475</t>
         </is>
       </c>
     </row>
@@ -1111,8 +1131,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91938172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>